--- a/data/eval/rag/技术支持评测数据集.xlsx
+++ b/data/eval/rag/技术支持评测数据集.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CodeFiles\WorkingDir\PythonProjects\LLM\wenda-agent\data\eval\rag\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CodeFiles\WorkingDir\PythonProjects\LLM\it-support-agent\data\eval\rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9745EA41-5EEA-43E8-A3F8-2FE67D3112C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AAFF93E-2CEA-420F-B96D-FBFB1B37A953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{2210621E-53D3-41E8-807B-6F213620F80C}"/>
   </bookViews>
@@ -34,21 +34,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>question</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ground_truth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户修改了虚机系统的“/dev/null”的权限值为775</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动 HDFS服务报错“Permission denied”是什么原因?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -136,6 +128,113 @@
 如果部署副本设置为1，性能完全依赖单个副本，且可靠性不足，单点故障会导致服务不可用；建议将副本数配置大于1，不仅能提升整体服务的并发处理能力，还能通过多副本冗余保证服务可靠性。
 推理性能与模型及推理框架紧密相关，选用带预置优化配置的推理引擎（如TensorRT-LLM、vLLM预置的模型优化配置），也可以通过模型压缩、量化、精简结构等方式优化模型，降低推理耗时。ModelArts中提供了模型资产管理的功能，方便溯源和模型反复调优。
 ModelArts提供了预置的推理服务镜像、模型资产，已经完成框架适配、参数调优，可直接一键部署。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引入 样例程序jar 包，Spark程序无法运行是什么原因？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行Spark任务时，引入的jar包不正确，导致Spark任务运行失败</t>
+  </si>
+  <si>
+    <t>提交 Spark 任务时报错“ClassNotFoundException”是什么原因？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spark WebUI 页面无法跳转到任务日志页面是什么原因？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置项“spark.httpdProxy.enable”未开启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hive 服务启动失败是什么原因？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. DBservice没有初始化好Hive的元数据库hivemeta。
+2. DBservice的浮动IP配置有误，导致metastore节点IP无法正确连接浮动IP，或者是在与该ip建立互信的时候失败导致metastore启动失败。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何在ModelArts 训练作业中加载部分训练好的参数？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在训练作业时，需要从预训练的模型中加载部分参数，初始化当前模型。请您通过如下方式加载：
+1. 通过如下代码，您可以查看所有的参数。from moxing.tensorflow.utils.hyper_param_flags import mox_flagsprint(mox_flags.get_help())
+2. 通过如下方式控制载入模型时需要恢复的参数名。其中，“checkpoint_include_patterns”为需要恢复的参数，“checkpoint_exclude_patterns”为不需要恢复的参数。checkpoint_include_patterns: Variables names patterns to include when restoring checkpoint. Such as:conv2d/weights.checkpoint_exclude_patterns: Variables names patterns to include when restoring checkpoint. Such as:conv2d/weights.
+3. 通过以下方式控制需要训练的参数列表。其中，“trainable_include_patterns为需要训练的参数列表，“trainable_exclude_patterns”为不需要训练的参数列表。--trainable_exclude_patterns: Variables names patterns to exclude for trainable variables. Such as:conv1,conv2.--trainable_include_patterns: Variables names patterns to include for trainable variables. Such as:logits.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在ModelArts 训练作业中如何判断文件夹是否复制完毕？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>您可以在训练作业启动文件的脚本中，通过如下方式获取复制和被复制文件夹大小，根据结果判断是否复制完毕：
+import moxing as mox mox.file.get_size('obs://bucket_name/obs_file',recursive=True)
+其中，“get_size”为获取文件或文件夹的大小。“recursive=True”表示类型为文件夹，“True”表示是文件夹，“False”为文件。
+如果输出结果为一致，表示文件夹复制已完毕。如果输出结果不一致，表示复制未结束。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hive客户端执行SQL失败，报错：Timed out waiting for a free availableconnection  是什么原因？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBService连接较多，获取连接超时。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动 HDFS服务报错“Permission denied”如何处理?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>步骤1 以root用户登录集群的任意一个Master节点。
+步骤2 登录成功后，执行 `chmod 666 /dev/null` 命令，修改“/dev/null”的权限值为“666”。
+步骤3 执行 `ls -al /dev/null` 命令，查看修改的“/dev/null”权限值是否为“666”，如果不是，需要修改为“666”。
+步骤4 修改成功后，重新启动HDFS。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flume启动后，Flume数据采集很慢是什么原因？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.  Flume堆内存设置不合理，导致Flume进程一直处于频繁GC。
+2.  用户业务配置的Spooldir source的deletePolicy策略是立即删除（immediate）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户配置的默认路径不正确，导致执行 Spark 作业时无法加载部分 jar，从而找不到对应的 class。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hive服务健康状态和Hive实例健康状态的区别是什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hive服务的健康状态（也就是在Manager界面看到的健康状态）有Good，Bad，Partially Healthy，Unknown四种状态 ，四种状态除了取决于Hive本身服务的可用性（会用简单的SQL来检测Hive服务的可用性），还取决于Hive服务所依赖的其他组件的服务状态。
+Hive实例分为Hiveserver和Metastore两种，健康状态有Good，Concerning ，Unknown三种状态，这三种状态是通过jmx通信来判定，与实例通信正常时为Good，通信异常时为Concerning，无法通信时为Unknown。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用 UDF 函数时提示“Invalid function” 是什么原因？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个HiveServer之间或者Hive与Spark之间共用的元数据未同步，导致不同HiveServer实例内存数据不一致，造成UDF不生效。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBS限制单次上传文件大小为5GB，TensorFlow保存summary可能是本地缓存，在每次触发flush时将该summary文件覆盖OBS上的原文件。当超过5GB后，由于达到了OBS单次导入文件大小的上限，导致无法继续写入。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModelArts训练作业在TensorFlow 向· OBS 写入 TensorBoard 到达 5GB 时停止是什么原因？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -506,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{574DA440-B759-47B2-9847-B6C9FB8C00B0}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="123.1328125" customWidth="1"/>
@@ -521,84 +620,172 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="97.15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="83.25" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="166.5" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="69.400000000000006" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="41.65" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="124.9" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="97.15" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
